--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 10/XKSX_DuAnVNSH03_SL200-SSD_121026.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 10/XKSX_DuAnVNSH03_SL200-SSD_121026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAD0913-F29B-4471-A6CA-35DD502EF61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1746D30-0DB9-47CE-AC8F-482DC150F408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,6 +504,21 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -563,21 +578,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -990,7 +990,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" customWidth="1"/>
@@ -1007,66 +1007,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="33" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="35"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="36" t="s">
+      <c r="A2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="36" t="s">
+      <c r="A3" s="32"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="37"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="38" t="s">
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="44"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="23"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="28"/>
     </row>
     <row r="6" spans="1:8" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
@@ -1136,21 +1136,21 @@
       <c r="A10" s="16">
         <v>1</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="22">
         <v>410</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="43" t="s">
+      <c r="H10" s="23" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1158,19 +1158,19 @@
       <c r="A11" s="16">
         <v>2</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="22">
         <v>820</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="43" t="s">
+      <c r="G11" s="45"/>
+      <c r="H11" s="23" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1178,19 +1178,19 @@
       <c r="A12" s="16">
         <v>3</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="22">
         <v>205</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="43" t="s">
+      <c r="G12" s="45"/>
+      <c r="H12" s="23" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1198,19 +1198,19 @@
       <c r="A13" s="16">
         <v>4</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="21" t="s">
         <v>31</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="22">
         <v>205</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="43" t="s">
+      <c r="G13" s="45"/>
+      <c r="H13" s="23" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1218,19 +1218,19 @@
       <c r="A14" s="16">
         <v>5</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="21" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="22">
         <v>205</v>
       </c>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="43" t="s">
+      <c r="G14" s="45"/>
+      <c r="H14" s="23" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1238,19 +1238,19 @@
       <c r="A15" s="16">
         <v>6</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="22">
         <v>205</v>
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="43" t="s">
+      <c r="G15" s="45"/>
+      <c r="H15" s="23" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1258,19 +1258,19 @@
       <c r="A16" s="16">
         <v>7</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="22">
         <v>820</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="16"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="43" t="s">
+      <c r="G16" s="45"/>
+      <c r="H16" s="23" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1278,19 +1278,19 @@
       <c r="A17" s="16">
         <v>8</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="21" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="22">
         <v>615</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="43" t="s">
+      <c r="G17" s="45"/>
+      <c r="H17" s="23" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1305,40 +1305,40 @@
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44" t="s">
+      <c r="B19" s="24"/>
+      <c r="C19" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44" t="s">
+      <c r="D19" s="24"/>
+      <c r="E19" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44" t="s">
+      <c r="F19" s="24"/>
+      <c r="G19" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H19" s="44"/>
+      <c r="H19" s="24"/>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45" t="s">
+      <c r="B20" s="25"/>
+      <c r="C20" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45" t="s">
+      <c r="D20" s="25"/>
+      <c r="E20" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45" t="s">
+      <c r="F20" s="25"/>
+      <c r="G20" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="45"/>
+      <c r="H20" s="25"/>
     </row>
     <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="17"/>
@@ -1391,22 +1391,22 @@
       <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="44"/>
+      <c r="B26" s="24"/>
       <c r="C26" s="18" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="7"/>
-      <c r="E26" s="44" t="s">
+      <c r="E26" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44" t="s">
+      <c r="F26" s="24"/>
+      <c r="G26" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H26" s="44"/>
+      <c r="H26" s="24"/>
     </row>
     <row r="27" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1432,24 +1432,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="G10:G17"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="G10:G17"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="82" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
